--- a/healthcare_forms/039_health_screening_agreement--healthcare_forms.xlsx
+++ b/healthcare_forms/039_health_screening_agreement--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>health_screening_agreement</t>
+          <t>health_screening_agreement_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Health Screening Agreement</t>
+          <t>Health Screening Agreement 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Signature Type</t>
+          <t>Manager Signature Type</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Manager Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1613,7 +1613,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>health_screening_agreement_choices</t>
+          <t>health_screening_agreement_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>health_screening_agreement_choices</t>
+          <t>health_screening_agreement_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
